--- a/decentralized-voting-system/server/config/random_emails_aadhaar_1000.xlsx
+++ b/decentralized-voting-system/server/config/random_emails_aadhaar_1000.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1005"/>
+  <dimension ref="A1:D1006"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14456,6 +14456,12 @@
       </c>
     </row>
     <row r="1005">
+      <c r="A1005" t="str">
+        <v/>
+      </c>
+      <c r="B1005" t="str">
+        <v/>
+      </c>
       <c r="C1005" t="str">
         <v>797971326008</v>
       </c>
@@ -14463,9 +14469,17 @@
         <v>a30488782@gmail.com</v>
       </c>
     </row>
+    <row r="1006">
+      <c r="C1006" t="str">
+        <v>797971334000</v>
+      </c>
+      <c r="D1006" t="str">
+        <v>bhatshreyas2004@gmail.com</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1005"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1006"/>
   </ignoredErrors>
 </worksheet>
 </file>